--- a/controle.xlsx
+++ b/controle.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="NFS_RECIBOS" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="IMPOSTOS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PARCELAS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +510,74 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>15/09/2026 22:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10.700,00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>teste aut nf</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>15/09/2026 23:04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>N° da NF</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Valor da Parcela</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Data Pagamento</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Assunto do Email</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Data Processamento</t>
         </is>
       </c>
     </row>

--- a/controle.xlsx
+++ b/controle.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,33 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Data Processamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10.700,00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>teste aut nf</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>15/09/2026 23:11</t>
         </is>
       </c>
     </row>
